--- a/data/trans_bre/P6907S1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 5,78</t>
+          <t>-17,02; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-22,69; 0,0</t>
+          <t>-23,06; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 13,28</t>
+          <t>-7,39; 13,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 21,38</t>
+          <t>-5,12; 20,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,23; 11,35</t>
+          <t>-12,5; 9,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 19,58</t>
+          <t>-7,92; 21,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,38; -1,2</t>
+          <t>-10,13; -1,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,87; 5,39</t>
+          <t>-16,27; 5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,58; 15,64</t>
+          <t>-15,6; 15,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-42,9; 0,0</t>
+          <t>-42,36; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 23,26</t>
+          <t>-8,28; 24,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 15,51</t>
+          <t>-11,93; 15,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 199,97</t>
+          <t>-53,2; 200,46</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 23,5</t>
+          <t>-7,28; 19,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,42; 42,04</t>
+          <t>-23,22; 46,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,89; 0,0</t>
+          <t>-14,37; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 0,0</t>
+          <t>-36,41; 0,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 855,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 63,54</t>
+          <t>-15,07; 58,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 0,0</t>
+          <t>-58,39; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,7; 0,0</t>
+          <t>-15,92; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 17,18</t>
+          <t>-22,44; 16,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-29,25; 0,0</t>
+          <t>-27,25; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -6,34</t>
+          <t>-36,48; -4,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -27,44</t>
+          <t>-95,41; -9,17</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 16,65</t>
+          <t>-10,73; 16,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,67</t>
+          <t>0,0; 17,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 8,41</t>
+          <t>-4,37; 7,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,47; 16,37</t>
+          <t>-9,53; 16,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 248,11</t>
+          <t>-64,4; 206,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 181,37</t>
+          <t>-49,01; 192,62</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 20,29</t>
+          <t>-0,17; 21,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,77; 0,0</t>
+          <t>-29,51; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 10,46</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,92; 585,43</t>
+          <t>-17,67; 680,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 6,84</t>
+          <t>-3,18; 6,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 2,17</t>
+          <t>-7,54; 2,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,08</t>
+          <t>-3,84; 2,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,68</t>
+          <t>-7,3; 2,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-26,04; 88,33</t>
+          <t>-29,84; 92,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 96,97</t>
+          <t>-100,0; 124,13</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 108,62</t>
+          <t>-80,6; 119,34</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 21,33</t>
+          <t>-54,59; 24,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6907S1-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P6907S1-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>8,06</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>166,92%</t>
+          <t>259,63%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-17,02; 5,26</t>
+          <t>-15,83; 6,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 0,0</t>
+          <t>-28,22; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 13,82</t>
+          <t>-8,01; 13,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 20,95</t>
+          <t>-3,02; 24,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-3,81</t>
+          <t>-3,47</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,94%</t>
+          <t>-41,6%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 9,38</t>
+          <t>-13,16; 11,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 21,95</t>
+          <t>-7,9; 19,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,13; -1,22</t>
+          <t>-10,42; -1,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 5,09</t>
+          <t>-15,61; 5,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 816,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 15,68</t>
+          <t>-16,14; 15,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-42,36; 0,0</t>
+          <t>-34,94; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,28; 24,18</t>
+          <t>-8,44; 28,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 15,18</t>
+          <t>-10,51; 14,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 200,46</t>
+          <t>-53,01; 198,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,34</t>
+          <t>-8,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-91,59%</t>
+          <t>-84,1%</t>
         </is>
       </c>
     </row>
@@ -960,27 +960,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 19,95</t>
+          <t>-8,31; 21,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-23,22; 46,43</t>
+          <t>-23,3; 42,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 0,0</t>
+          <t>-16,17; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 0,53</t>
+          <t>-33,05; 1,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 855,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,68</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 58,23</t>
+          <t>-15,47; 60,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-58,39; 0,0</t>
+          <t>-50,72; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 0,0</t>
+          <t>-14,46; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-19,86</t>
+          <t>-18,48</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-77,99%</t>
+          <t>-77,26%</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 16,57</t>
+          <t>-21,57; 14,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 0,0</t>
+          <t>-27,69; 0,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-36,48; -4,55</t>
+          <t>-34,09; -3,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,41; -9,17</t>
+          <t>-94,97; 0,04</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,74</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 16,02</t>
+          <t>-9,72; 16,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,4</t>
+          <t>0,0; 14,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 7,91</t>
+          <t>-5,36; 7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 16,08</t>
+          <t>-9,19; 15,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 206,02</t>
+          <t>-64,51; 238,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,01; 192,62</t>
+          <t>-46,64; 159,92</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,16</t>
+          <t>3,45</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,12 +1360,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 21,65</t>
+          <t>-0,46; 22,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 0,0</t>
+          <t>-27,43; 0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1375,12 +1375,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,46</t>
+          <t>0,0; 12,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 680,14</t>
+          <t>-26,65; 665,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-24,84%</t>
+          <t>-10,17%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 6,98</t>
+          <t>-3,3; 6,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 2,45</t>
+          <t>-7,32; 2,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,32</t>
+          <t>-3,64; 2,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 2,18</t>
+          <t>-5,85; 3,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 92,78</t>
+          <t>-30,46; 93,45</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 124,13</t>
+          <t>-100,0; 136,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-80,6; 119,34</t>
+          <t>-81,34; 125,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-54,59; 24,96</t>
+          <t>-43,39; 44,49</t>
         </is>
       </c>
     </row>
